--- a/data/MyCareer_Process Flow.xlsx
+++ b/data/MyCareer_Process Flow.xlsx
@@ -1,23 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gommt-my.sharepoint.com/personal/mmt12354_go-mmt_com/Documents/Agent A Thon/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="8_{76DF5C1C-E0A4-45B8-9118-FD92C6ACB336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C902770-28AB-44B1-958C-1F1E476B15A5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FB00608-AF72-4CB7-89B2-7DA51E1E5CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{98C84C59-75D2-4C84-9ACF-57E378B859ED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{98C84C59-75D2-4C84-9ACF-57E378B859ED}"/>
   </bookViews>
   <sheets>
-    <sheet name="Workflow" sheetId="1" r:id="rId1"/>
-    <sheet name="Competency" sheetId="2" r:id="rId2"/>
-    <sheet name="Career Paths" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Old Workflow" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Revised Workflow" sheetId="6" r:id="rId2"/>
+    <sheet name="UIUX - Employee" sheetId="7" r:id="rId3"/>
+    <sheet name="UIUX - Manager" sheetId="8" r:id="rId4"/>
+    <sheet name="Role-Competency Mapping" sheetId="2" r:id="rId5"/>
+    <sheet name="Competency vs Level Definitions" sheetId="5" r:id="rId6"/>
+    <sheet name="Probable Career Paths" sheetId="3" r:id="rId7"/>
+    <sheet name="Role Plays" sheetId="4" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Role-Competency Mapping'!$A$1:$J$8</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,9 +49,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="98">
-  <si>
-    <t>BD/KAM Ecosystem - BDMs, KAMs, ZMs, Category, Lead Category Manager</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="211">
+  <si>
+    <t>BD/KAM Ecosystem - BDMs, KAMs, ZMs, Category, Category Supply</t>
   </si>
   <si>
     <t>Level 1 (9 skills)</t>
@@ -177,6 +184,219 @@
     <t>Validate score</t>
   </si>
   <si>
+    <t>Level 1</t>
+  </si>
+  <si>
+    <t>Reporting Manager to share inputs for their reportees</t>
+  </si>
+  <si>
+    <t>Mandatory for everyone, till the time inputs for all employees is filled in, we won't launch the initiative</t>
+  </si>
+  <si>
+    <t>BD Competency Profile</t>
+  </si>
+  <si>
+    <t>Annual Appraisal from Darwin fed into the system at the backend</t>
+  </si>
+  <si>
+    <t>Last Appraisal Cycle, extracted in a form of a report</t>
+  </si>
+  <si>
+    <t>Interview  Feedback fed into the system at the backend</t>
+  </si>
+  <si>
+    <t>For employees who are less than a year in the system, extracted manually from employee profiles individually</t>
+  </si>
+  <si>
+    <t>Skip Level Manager to validate the above data</t>
+  </si>
+  <si>
+    <t>Can view a consolidated view of input layer 1,2,3</t>
+  </si>
+  <si>
+    <t>Employee completes skill assessment as well as role plays</t>
+  </si>
+  <si>
+    <t>No weightage given to emp, manager inputs. Suggestions for the emp will be given as per this step. Skill assessment (adaptive style) &amp; role plays to be done for all 7 skills</t>
+  </si>
+  <si>
+    <t>Estimating Confidence Score</t>
+  </si>
+  <si>
+    <t>Contextual analysis utilizing emp competency assessment, reporting manager plus variable score. Only for HRBP consumption</t>
+  </si>
+  <si>
+    <t>Level 2</t>
+  </si>
+  <si>
+    <t>BD Compentency Profile (Skill vs Proficiency Levels)</t>
+  </si>
+  <si>
+    <t>Compare BD Competency Profile &lt; Sales Persona, Emp first closes that gap before moving to the higher proficiency levels (refer Table 1, "probable career path" tab)</t>
+  </si>
+  <si>
+    <t>Career map with Learning Journeys</t>
+  </si>
+  <si>
+    <t>Sales Personas (BDM, KAM, ZM)</t>
+  </si>
+  <si>
+    <t>Compare BD Competency Profile = Their own Sales Persona, Emp can start working on their probable paths (greens and greys)</t>
+  </si>
+  <si>
+    <t>Career Map</t>
+  </si>
+  <si>
+    <t>Create a career map/web wrt "probable career path" tab inputs (refer Table2; green ones to be enabled, grey ones are to be locked)</t>
+  </si>
+  <si>
+    <t>Course Recommendations</t>
+  </si>
+  <si>
+    <t>Employee shops courses (logic already shared with Armeen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MyMentor Platform </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map mentor only if emp is moving to next level/grade, else no mentorship </t>
+  </si>
+  <si>
+    <t>Level 3</t>
+  </si>
+  <si>
+    <t>Employee starts learning journeys</t>
+  </si>
+  <si>
+    <t>Gamified Leaderboards - Employee Portal, Email</t>
+  </si>
+  <si>
+    <t>Dashboards</t>
+  </si>
+  <si>
+    <t>Dashboards - Reporting Manager,  Skip Level Manager and Admin</t>
+  </si>
+  <si>
+    <t>Nudges - Employee Portal, Email to Reporting Managers</t>
+  </si>
+  <si>
+    <t>Level 4</t>
+  </si>
+  <si>
+    <t>Skip Level Manager to validate last 6 months journey (Recalibration)</t>
+  </si>
+  <si>
+    <t>RD gets to see the learning completion status (Red-Amber-Green) and now he/she shares the new assessment</t>
+  </si>
+  <si>
+    <t>BD Competency Level New</t>
+  </si>
+  <si>
+    <t>Employee Interface</t>
+  </si>
+  <si>
+    <t>Welcome Screen</t>
+  </si>
+  <si>
+    <t>Why this? Mention objective of the project</t>
+  </si>
+  <si>
+    <t>Careers @ MMT , but add a disclaimer that it doesnt guarantee a promotion</t>
+  </si>
+  <si>
+    <t>Career lattice</t>
+  </si>
+  <si>
+    <t>Personalised carrer progression, basis role and person</t>
+  </si>
+  <si>
+    <t>Embed the policy document - career lattice</t>
+  </si>
+  <si>
+    <t>Assesment</t>
+  </si>
+  <si>
+    <t>Role Plays and Quizzes</t>
+  </si>
+  <si>
+    <t>Assesment result sceeen</t>
+  </si>
+  <si>
+    <t>Result would be basis back end logic</t>
+  </si>
+  <si>
+    <t>Employee input to not be consider</t>
+  </si>
+  <si>
+    <t>Possibilty 1</t>
+  </si>
+  <si>
+    <t>You are doing great, but first let's focus in getting better at your current role, lets work on that (make it palatable)</t>
+  </si>
+  <si>
+    <t>Possibilty 2</t>
+  </si>
+  <si>
+    <t>Great, going good, lets hone you for KAM/ZM role, in case of this, take employee input as possible career progression</t>
+  </si>
+  <si>
+    <t>Learning Journey</t>
+  </si>
+  <si>
+    <t>Add to cart journey, make custom learning path</t>
+  </si>
+  <si>
+    <t>Add mentor, only in case of career progression (grade up)</t>
+  </si>
+  <si>
+    <t>Learning Dashboard</t>
+  </si>
+  <si>
+    <t>Gamified Leaderboard</t>
+  </si>
+  <si>
+    <t>Progress Bar</t>
+  </si>
+  <si>
+    <t>Congralutions (Party Poppers)</t>
+  </si>
+  <si>
+    <t>Color Scheme - MMT red, blue, grey, white.</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>Why this?</t>
+  </si>
+  <si>
+    <t>Why get BDs to learn</t>
+  </si>
+  <si>
+    <t>Prioritize this and give them time to study</t>
+  </si>
+  <si>
+    <t>Employee scoring</t>
+  </si>
+  <si>
+    <t>Get the slider with description</t>
+  </si>
+  <si>
+    <t>Get Manager inputs on screen</t>
+  </si>
+  <si>
+    <t>Get contextual data from TNA and Appraisal</t>
+  </si>
+  <si>
+    <t>Manager Dashborrd</t>
+  </si>
+  <si>
+    <t>Manager Dashboard</t>
+  </si>
+  <si>
     <t>Competencies</t>
   </si>
   <si>
@@ -186,31 +406,25 @@
     <t>Definitions/Notes</t>
   </si>
   <si>
-    <t>BDM (RL1-2)</t>
-  </si>
-  <si>
-    <t>BDM (RL3-4)</t>
-  </si>
-  <si>
-    <t>KAM (RL1-2)</t>
-  </si>
-  <si>
-    <t>KAM (RL3-4)</t>
-  </si>
-  <si>
-    <t>ZM (RL5-6)</t>
-  </si>
-  <si>
-    <t>Category Manager (RL3-4)</t>
-  </si>
-  <si>
-    <t>Supply Category (BDFE (RL2-4)</t>
-  </si>
-  <si>
-    <t>(Sales)</t>
-  </si>
-  <si>
-    <t>(Product)</t>
+    <t>BDM (RL2-3)</t>
+  </si>
+  <si>
+    <t>BDM (RL4)</t>
+  </si>
+  <si>
+    <t>KAM (RL2-3)</t>
+  </si>
+  <si>
+    <t>KAM (RL4)</t>
+  </si>
+  <si>
+    <t>ZM(RL4-5)</t>
+  </si>
+  <si>
+    <t>ZM (RL6)</t>
+  </si>
+  <si>
+    <t>RD (RL7-8)</t>
   </si>
   <si>
     <t>Communication</t>
@@ -219,10 +433,7 @@
     <t>Behavioral</t>
   </si>
   <si>
-    <t>Includes written and verbal communication, negotiation updates, presentation skills, and regular partner communication.</t>
-  </si>
-  <si>
-    <t>Includes partner business reviews, insight sharing, and structured communication of pricing/inventory actions.</t>
+    <t>Includes written and verbal communication, negotiation &amp; influencing skills, presentation skills, regular partner communication</t>
   </si>
   <si>
     <t>Intermediate</t>
@@ -234,34 +445,34 @@
     <t>Advanced</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>Stakeholder Management</t>
   </si>
   <si>
-    <t>Coordinates with revenue, marketing, product, operations, finance, and hotel partners.</t>
-  </si>
-  <si>
-    <t>Aligns internal teams around pricing, inventory, campaigns, invoices, and partner issue closure.</t>
+    <t>Coordinates with  cross functional teams, manages expectations and conflict resolution</t>
   </si>
   <si>
     <t>Ownership &amp; Accountability</t>
   </si>
   <si>
-    <t>Takes end-to-end ownership of account outcomes, KRAs, follow-ups, and partner commitments.</t>
-  </si>
-  <si>
-    <t>Owns performance across growth, parity, inventory depth, program adoption, and review cadence.</t>
+    <t>Takes end-to-end ownership of outcomes, KRAs, follow-ups, and partner commitments</t>
+  </si>
+  <si>
+    <t>Beginner</t>
   </si>
   <si>
     <t>Team Management</t>
   </si>
   <si>
-    <t>Provides direction, manages team performance, reviews KRAs, and supports career development.</t>
-  </si>
-  <si>
-    <t>Includes coaching BDMs/KAMs on market priorities, partner conversations, and execution discipline.</t>
-  </si>
-  <si>
-    <t>Beginner</t>
+    <t>Provides direction, manages team expectations and performance, reviews KRAs, and supports career development.</t>
+  </si>
+  <si>
+    <t>Executive Presence</t>
+  </si>
+  <si>
+    <t>To inspire trust and confidence in your team and leadership</t>
   </si>
   <si>
     <t>Consultative Selling</t>
@@ -270,64 +481,244 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>Understands hotel needs, recommends solutions, and pitches relevant commercial/program levers.</t>
-  </si>
-  <si>
-    <t>Connects partner problems to MMT levers such as parity, adtech, inventory, True Flexi, and drives.</t>
+    <t>Understands partner needs, recommends solutions, and- pitches relevant commercial/program levers</t>
   </si>
   <si>
     <t>Data Analytics</t>
   </si>
   <si>
-    <t>Analyzes production reports, MIS, market intelligence, and portfolio trends to recommend action.</t>
-  </si>
-  <si>
-    <t>Understands metrics such as RN/GMV growth, price parity, inventory depth, adtech, invoice upload, and response rate.</t>
-  </si>
-  <si>
-    <t>Portfolio Growth</t>
-  </si>
-  <si>
-    <t>Drives growth for assigned market/account portfolio through business plans and regular reviews.</t>
-  </si>
-  <si>
-    <t>Includes RN growth, GMV growth, supply targets, portfolio productivity, and market opportunity identification.</t>
-  </si>
-  <si>
-    <t>Price Parity Management</t>
-  </si>
-  <si>
-    <t>Manages MnB parity, OTA comparison, floor/cap target understanding, and partner correction actions.</t>
-  </si>
-  <si>
-    <t>Includes Booking, Agoda, CTP, Genius L2/L3, and DND Hotels Meta parity where applicable.</t>
-  </si>
-  <si>
-    <t>Business Acumen</t>
-  </si>
-  <si>
-    <t>Understands business levers, customer behavior, revenue drivers, margin, conversion, and category economics.</t>
-  </si>
-  <si>
-    <t>Roles</t>
+    <t>Analyzes data, reports, MIS, market intelligence, and portfolio trends to recommend action</t>
+  </si>
+  <si>
+    <r>
+      <t>Beginner:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Learns fundamentals, performs routine tasks with guidance.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Intermediate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Works independently on standard responsibilities and solves routine problems.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Proficient:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Consistently delivers strong results, influences others, and handles complex situations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Advanced:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Shapes strategy, influences senior leaders, drives organizational impact, and develops others.</t>
+    </r>
+  </si>
+  <si>
+    <t>Competency</t>
+  </si>
+  <si>
+    <t>Communicates clearly in routine interactions.</t>
+  </si>
+  <si>
+    <t>Adapts communication for different audiences and navigates discussions.</t>
+  </si>
+  <si>
+    <t>Influences stakeholders through persuasive communication and negotiations.</t>
+  </si>
+  <si>
+    <t>Shapes strategic conversations and inspires confidence with senior leaders.</t>
+  </si>
+  <si>
+    <t>Builds positive relationships with assigned partners.</t>
+  </si>
+  <si>
+    <t>Manages partner expectations, resolves routine issues maintains regular engagement.</t>
+  </si>
+  <si>
+    <t>Builds trusted partnerships, influences partner decisions, and drives business outcomes.</t>
+  </si>
+  <si>
+    <t>Develops strategic partner relationships and influences long-term growth.</t>
+  </si>
+  <si>
+    <t>Delivers assigned tasks on time with accountability.</t>
+  </si>
+  <si>
+    <t>Independently owns tasks and manages risks.</t>
+  </si>
+  <si>
+    <t>Drives end-to-end business outcomes and continuous improvement.</t>
+  </si>
+  <si>
+    <t>Owns strategic initiatives and fosters a culture of accountability.</t>
+  </si>
+  <si>
+    <t>Collaborates effectively and supports team goals.</t>
+  </si>
+  <si>
+    <t>Coaches junior team members and delegates work effectively.</t>
+  </si>
+  <si>
+    <t>Manages performance, develops talent, and builds high-performing teams.</t>
+  </si>
+  <si>
+    <t>Develops leaders, drives organizational effectiveness, and leads through change.</t>
+  </si>
+  <si>
+    <t>Demonstrates professionalism and confidence.</t>
+  </si>
+  <si>
+    <t>Builds credibility through confident communication and execution.</t>
+  </si>
+  <si>
+    <t>Influences senior audiences with composure and sound judgment.</t>
+  </si>
+  <si>
+    <t>Serves as a trusted advisor and shapes strategic decisions.</t>
+  </si>
+  <si>
+    <t>Understands partner needs through basic questioning, explains relevant products or programs, and supports sales conversations.</t>
+  </si>
+  <si>
+    <t>Identifies business challenges, recommends appropriate solutions, and tailors proposals to partner requirements while handling standard objections.</t>
+  </si>
+  <si>
+    <t>Acts as a trusted advisor by uncovering strategic opportunities, developing value-based solutions, influencing partner decisions, and driving commercial outcomes</t>
+  </si>
+  <si>
+    <t>Shapes partner strategy, creates innovative commercial solutions, influences executive decision-makers, and drives transformational, long-term business gro</t>
+  </si>
+  <si>
+    <t>Uses reports to monitor performance and identify trends.</t>
+  </si>
+  <si>
+    <t>Analyzes data to generate actionable insights.</t>
+  </si>
+  <si>
+    <t>Uses analytics to drive decisions and identify opportunities.</t>
+  </si>
+  <si>
+    <t>Builds analytical frameworks that influence strategic decisions.</t>
+  </si>
+  <si>
+    <t>Table 1</t>
+  </si>
+  <si>
+    <t>Internal System Logic to suggest learning</t>
+  </si>
+  <si>
+    <t>Role &amp; Grades</t>
+  </si>
+  <si>
+    <t>KAM(RL2-3)</t>
   </si>
   <si>
     <t>ZM (RL4-5)</t>
   </si>
   <si>
-    <t>NA</t>
+    <t>BDM (RL2)</t>
+  </si>
+  <si>
+    <t>Ideal Profile</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
+    <t>BDM (RL3)</t>
+  </si>
+  <si>
+    <t>Comapre with ideal only if gap is 2 or more level</t>
+  </si>
+  <si>
+    <t>Comapre with next, if gap with ideal is 1 or less</t>
+  </si>
+  <si>
+    <t>KAM (RL2)</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>KAM (RL3)</t>
+  </si>
+  <si>
+    <t>ZM (RL4)</t>
+  </si>
+  <si>
+    <t>ZM to RD movement won't happen via this portal. There will be structured learning journeys</t>
+  </si>
+  <si>
+    <t>ZM (RL5)</t>
+  </si>
+  <si>
+    <t>RD (RL7)</t>
+  </si>
+  <si>
+    <t>RD (RL8)</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Suggestion on Employee Portal</t>
+  </si>
+  <si>
+    <t>C%XZA</t>
+  </si>
+  <si>
+    <t>KAM</t>
+  </si>
+  <si>
+    <t>ZM</t>
+  </si>
+  <si>
+    <t>Not to be suggested</t>
+  </si>
+  <si>
+    <t>Grey/Locked Future</t>
   </si>
   <si>
     <t>Skill</t>
   </si>
   <si>
-    <t>RolePlay</t>
+    <t>RolePlay Situation</t>
   </si>
   <si>
     <t>https://www.linkedin.com/learning/role-play/scenarios/urn:li:la_rolePlayScenario:urn:li:llsServeScenario:127526908?u=236676260</t>
@@ -337,13 +728,16 @@
   </si>
   <si>
     <t>https://www.linkedin.com/learning/role-play/scenarios/urn:li:la_rolePlayScenario:urn:li:llsServeScenario:127537771?u=236676260</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/learning/role-play/scenarios/urn:li:la_rolePlayScenario:urn:li:llsServeSce…</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,12 +759,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -395,8 +783,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,8 +825,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -431,6 +865,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -572,6 +1041,15 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -627,10 +1105,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -638,139 +1170,228 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -778,22 +1399,72 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -829,7 +1500,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Arrow: Right 9">
+        <xdr:cNvPr id="20" name="Arrow: Right 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D1EEA67-1FFA-43B2-8880-EAC18B720CCA}"/>
@@ -895,7 +1566,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Arrow: Right 10">
+        <xdr:cNvPr id="21" name="Arrow: Right 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{051EFE13-5FF2-4C4C-908A-741BA7F76A23}"/>
@@ -961,7 +1632,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Arrow: Right 11">
+        <xdr:cNvPr id="22" name="Arrow: Right 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB5049CC-DCC1-4EE1-93EE-9DC151A128DD}"/>
@@ -1027,7 +1698,7 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Arrow: Right 12">
+        <xdr:cNvPr id="23" name="Arrow: Right 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE347622-3A79-4CA4-96BB-B83B3454B829}"/>
@@ -1069,6 +1740,374 @@
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3209324</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>25743</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3415270</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>171622</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Arrow: Down 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A81C63E-115F-2188-DDB8-F8A3FC658C6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7311081" y="1776284"/>
+          <a:ext cx="205946" cy="326081"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3198683</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>32265</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3404629</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>178144</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Arrow: Down 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E92A2489-5027-4C2F-97E1-25A12BAC653A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7300440" y="3396049"/>
+          <a:ext cx="205946" cy="326081"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3179462</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38786</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3385408</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>4462</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Arrow: Down 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81EDC850-F5B9-46FF-9108-AA433FA4D267}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7281219" y="4672570"/>
+          <a:ext cx="205946" cy="326081"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180204</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>94392</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>798044</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>68649</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Arrow: Curved Up 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1310C61-EC78-0CD2-7ECA-B45B7F191CAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000">
+          <a:off x="13776927" y="3771385"/>
+          <a:ext cx="2685879" cy="617840"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedUpArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>550635</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>146678</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>101879</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>134467</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Right Brace 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA881CF7-56D9-A73F-77F0-A90F3E9B24AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8716735" y="1213478"/>
+          <a:ext cx="186244" cy="749789"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
@@ -1399,57 +2438,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F254CB3-FB5D-4562-9FCC-8973A4BE105A}">
   <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
-    <col min="7" max="7" width="22.28515625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="34.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="2"/>
-    <col min="11" max="11" width="14.5703125" style="11" customWidth="1"/>
-    <col min="12" max="12" width="25.85546875" style="11" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" style="11" customWidth="1"/>
-    <col min="14" max="14" width="17.42578125" style="11" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="2.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="7" max="7" width="31.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="1"/>
+    <col min="11" max="11" width="14.5703125" style="12" customWidth="1"/>
+    <col min="12" max="12" width="25.85546875" style="12" customWidth="1"/>
+    <col min="13" max="13" width="23.5703125" style="12" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" style="12" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="11" customFormat="1">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19" t="s">
+    <row r="1" spans="1:14" s="12" customFormat="1">
+      <c r="A1" s="20"/>
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="1:14" ht="15" thickBot="1">
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" ht="15" thickBot="1">
-      <c r="B3" s="44" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1">
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1">
+      <c r="B3" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="46"/>
-      <c r="G3" s="30" t="s">
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="90"/>
+      <c r="G3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="32"/>
-      <c r="K3" s="30" t="s">
+      <c r="H3" s="74"/>
+      <c r="I3" s="75"/>
+      <c r="K3" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="31"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1">
+      <c r="L3" s="74"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
@@ -1462,435 +2501,435 @@
       <c r="E4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" s="4" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B5" s="33">
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B5" s="76">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="38" t="s">
+      <c r="H5" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="38" t="s">
+      <c r="K5" s="81" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="38" t="s">
+      <c r="M5" s="81" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="4" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B6" s="34"/>
+    <row r="6" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B6" s="77"/>
       <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="43"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="25" t="s">
+      <c r="D6" s="82"/>
+      <c r="E6" s="95"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="39"/>
-    </row>
-    <row r="7" spans="1:14" s="4" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B7" s="34"/>
+      <c r="M6" s="82"/>
+    </row>
+    <row r="7" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B7" s="77"/>
       <c r="C7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="43"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="26" t="s">
+      <c r="D7" s="82"/>
+      <c r="E7" s="95"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M7" s="39"/>
-    </row>
-    <row r="8" spans="1:14" s="4" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B8" s="41"/>
+      <c r="M7" s="82"/>
+    </row>
+    <row r="8" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B8" s="84"/>
       <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="40"/>
-      <c r="E8" s="43"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="38" t="s">
+      <c r="D8" s="83"/>
+      <c r="E8" s="95"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="25" t="s">
+      <c r="I8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="39"/>
-    </row>
-    <row r="9" spans="1:14" s="4" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="B9" s="33">
+      <c r="M8" s="82"/>
+    </row>
+    <row r="9" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B9" s="76">
         <v>2</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="40"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="25" t="s">
+      <c r="E9" s="82"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="83"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="M9" s="39"/>
-    </row>
-    <row r="10" spans="1:14" s="4" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B10" s="34"/>
+      <c r="M9" s="82"/>
+    </row>
+    <row r="10" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B10" s="77"/>
       <c r="C10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="G10" s="39" t="s">
+      <c r="D10" s="82"/>
+      <c r="E10" s="82"/>
+      <c r="G10" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39" t="s">
+      <c r="H10" s="82"/>
+      <c r="I10" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="39"/>
-      <c r="L10" s="27" t="s">
+      <c r="K10" s="82"/>
+      <c r="L10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="39"/>
-    </row>
-    <row r="11" spans="1:14" s="4" customFormat="1" ht="13.5" thickBot="1">
-      <c r="B11" s="34"/>
+      <c r="M10" s="82"/>
+    </row>
+    <row r="11" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B11" s="77"/>
       <c r="C11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="M11" s="39"/>
-    </row>
-    <row r="12" spans="1:14" s="4" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
-      <c r="B12" s="41"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="82"/>
+      <c r="K11" s="82"/>
+      <c r="M11" s="82"/>
+    </row>
+    <row r="12" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B12" s="84"/>
       <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="38" t="s">
+      <c r="D12" s="83"/>
+      <c r="E12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="39"/>
-    </row>
-    <row r="13" spans="1:14" s="4" customFormat="1" ht="13.5" customHeight="1">
-      <c r="B13" s="47">
+      <c r="I12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="82"/>
+    </row>
+    <row r="13" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1">
+      <c r="B13" s="91">
         <v>3</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="39"/>
-    </row>
-    <row r="14" spans="1:14" s="4" customFormat="1" ht="13.5" thickBot="1">
-      <c r="B14" s="48"/>
+      <c r="E13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="82"/>
+    </row>
+    <row r="14" spans="1:14" s="3" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B14" s="92"/>
       <c r="C14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="40"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="K14" s="83"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="83"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="N15" s="2"/>
+      <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="N16" s="2"/>
+      <c r="N16" s="1"/>
     </row>
     <row r="17" spans="6:14">
-      <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="6:14" ht="15" thickBot="1">
-      <c r="N18" s="2"/>
-    </row>
-    <row r="19" spans="6:14" ht="15" thickBot="1">
-      <c r="F19" s="30" t="s">
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="6:14" ht="15.75" thickBot="1">
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="6:14" ht="15.75" thickBot="1">
+      <c r="F19" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="32"/>
-      <c r="N19" s="2"/>
-    </row>
-    <row r="20" spans="6:14" ht="15" thickBot="1">
-      <c r="F20" s="8" t="s">
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="75"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="6:14" ht="15.75" thickBot="1">
+      <c r="F20" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" s="1"/>
     </row>
     <row r="21" spans="6:14">
-      <c r="F21" s="33">
+      <c r="F21" s="76">
         <v>1</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="38" t="s">
+      <c r="I21" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="N21" s="2"/>
+      <c r="N21" s="1"/>
     </row>
     <row r="22" spans="6:14">
-      <c r="F22" s="34"/>
+      <c r="F22" s="77"/>
       <c r="G22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="39"/>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="6:14" ht="15" thickBot="1">
-      <c r="F23" s="34"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="82"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="6:14" ht="15.75" thickBot="1">
+      <c r="F23" s="77"/>
       <c r="G23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="37"/>
-      <c r="I23" s="39"/>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="6:14" ht="14.45" customHeight="1">
-      <c r="F24" s="33">
+      <c r="H23" s="80"/>
+      <c r="I23" s="82"/>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="6:14" ht="15" customHeight="1">
+      <c r="F24" s="76">
         <v>2</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="39" t="s">
+      <c r="H24" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="N24" s="2"/>
+      <c r="I24" s="82"/>
+      <c r="N24" s="1"/>
     </row>
     <row r="25" spans="6:14">
-      <c r="F25" s="34"/>
+      <c r="F25" s="77"/>
       <c r="G25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H25" s="39"/>
-      <c r="I25" s="39"/>
-      <c r="N25" s="2"/>
-    </row>
-    <row r="26" spans="6:14">
-      <c r="F26" s="34"/>
+      <c r="H25" s="82"/>
+      <c r="I25" s="82"/>
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="6:14" ht="15" customHeight="1">
+      <c r="F26" s="77"/>
       <c r="G26" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="39"/>
-      <c r="I26" s="39"/>
-      <c r="N26" s="2"/>
-    </row>
-    <row r="27" spans="6:14" ht="15" thickBot="1">
-      <c r="F27" s="41"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="6:14" ht="15.75" thickBot="1">
+      <c r="F27" s="84"/>
       <c r="G27" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="40"/>
-      <c r="I27" s="39"/>
-      <c r="N27" s="2"/>
-    </row>
-    <row r="28" spans="6:14" ht="26.45" thickBot="1">
-      <c r="F28" s="33">
+      <c r="H27" s="83"/>
+      <c r="I27" s="82"/>
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="6:14" ht="27.75" thickBot="1">
+      <c r="F28" s="76">
         <v>3</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="G28" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="33" t="s">
+      <c r="H28" s="76" t="s">
         <v>43</v>
       </c>
-      <c r="I28" s="39"/>
-      <c r="N28" s="2"/>
+      <c r="I28" s="82"/>
+      <c r="N28" s="1"/>
     </row>
     <row r="29" spans="6:14">
-      <c r="F29" s="34"/>
+      <c r="F29" s="77"/>
       <c r="G29" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H29" s="34"/>
-      <c r="I29" s="39"/>
-      <c r="N29" s="2"/>
-    </row>
-    <row r="30" spans="6:14" ht="15" thickBot="1">
-      <c r="F30" s="41"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="82"/>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="6:14" ht="15.75" thickBot="1">
+      <c r="F30" s="84"/>
       <c r="G30" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="41"/>
-      <c r="I30" s="40"/>
-      <c r="N30" s="2"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="83"/>
+      <c r="N30" s="1"/>
     </row>
     <row r="31" spans="6:14">
-      <c r="N31" s="2"/>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="6:14">
-      <c r="N32" s="2"/>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="3:14">
-      <c r="N33" s="2"/>
+      <c r="N33" s="1"/>
     </row>
     <row r="34" spans="3:14">
-      <c r="N34" s="2"/>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" spans="3:14">
-      <c r="N35" s="2"/>
+      <c r="N35" s="1"/>
     </row>
     <row r="36" spans="3:14">
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
     </row>
     <row r="37" spans="3:14">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" spans="3:14">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" spans="3:14">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
     </row>
     <row r="40" spans="3:14">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E14"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="B5:B8"/>
-    <mergeCell ref="I5:I9"/>
-    <mergeCell ref="I10:I14"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E14"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="K5:K14"/>
     <mergeCell ref="M5:M14"/>
     <mergeCell ref="H8:H11"/>
-    <mergeCell ref="H12:H14"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="G5:G9"/>
     <mergeCell ref="G10:G14"/>
+    <mergeCell ref="I5:I9"/>
+    <mergeCell ref="I10:I14"/>
+    <mergeCell ref="H12:H14"/>
     <mergeCell ref="F19:I19"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="H21:H23"/>
@@ -1906,375 +2945,602 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8ABEF94-B3DE-46A7-AA17-C522D7D14E74}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDF316A-AF5E-4C18-9F73-3DB6D73C23F2}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="13"/>
-    <col min="3" max="3" width="47.42578125" style="16" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" style="15" customWidth="1"/>
-    <col min="5" max="8" width="10" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="13" customWidth="1"/>
-    <col min="11" max="11" width="14" style="13" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="6.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="129.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" style="16" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="12" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="25.5" customHeight="1">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5" s="12" customFormat="1">
+      <c r="A1" s="20"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" s="3" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A5" s="60">
+        <v>1</v>
+      </c>
+      <c r="B5" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C5" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="20" t="s">
+      <c r="D5" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="20" t="s">
+    </row>
+    <row r="6" spans="1:5" s="3" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A6" s="60">
+        <v>2</v>
+      </c>
+      <c r="B6" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="C6" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="D6" s="71"/>
+    </row>
+    <row r="7" spans="1:5" s="3" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A7" s="60">
+        <v>3</v>
+      </c>
+      <c r="B7" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="C7" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="D7" s="71"/>
+    </row>
+    <row r="8" spans="1:5" s="3" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A8" s="60">
+        <v>4</v>
+      </c>
+      <c r="B8" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="C8" s="61" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="C2" s="16" t="s">
+      <c r="D8" s="71"/>
+    </row>
+    <row r="9" spans="1:5" s="3" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A9" s="60">
+        <v>5</v>
+      </c>
+      <c r="B9" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="C9" s="61" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="24">
-      <c r="A3" s="13" t="s">
+      <c r="D9" s="71"/>
+    </row>
+    <row r="10" spans="1:5" s="3" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A10" s="60">
+        <v>6</v>
+      </c>
+      <c r="B10" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C10" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="D10" s="72"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="13.5" customHeight="1">
+      <c r="A15" s="60">
+        <v>1</v>
+      </c>
+      <c r="B15" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="C15" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="D15" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="13" t="s">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="60">
+        <v>2</v>
+      </c>
+      <c r="B16" s="58" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="24">
-      <c r="A4" s="13" t="s">
+      <c r="C16" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="D16" s="71"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="60">
+        <v>3</v>
+      </c>
+      <c r="B17" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C17" s="61" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="24">
-      <c r="A5" s="13" t="s">
+      <c r="D17" s="71"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="60">
+        <v>4</v>
+      </c>
+      <c r="B18" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="C18" s="61" t="s">
         <v>67</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D18" s="71"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="60">
+        <v>5</v>
+      </c>
+      <c r="B19" s="58" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="24">
-      <c r="A6" s="13" t="s">
+      <c r="C19" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="D19" s="72"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="13"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="67" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="B22" s="67"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="63">
+        <v>1</v>
+      </c>
+      <c r="B24" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="C24" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="24">
-      <c r="A7" s="13" t="s">
+      <c r="D24" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="63">
+        <v>2</v>
+      </c>
+      <c r="B25" s="68"/>
+      <c r="C25" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="D25" s="69"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="63">
+        <v>3</v>
+      </c>
+      <c r="B26" s="68"/>
+      <c r="C26" s="65" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D26" s="69"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="13"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="24">
-      <c r="A8" s="13" t="s">
+      <c r="B29" s="67"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="59" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" ht="18.600000000000001" customHeight="1">
+      <c r="A31" s="60">
+        <v>1</v>
+      </c>
+      <c r="B31" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="C31" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D31" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="24">
-      <c r="A9" s="13" t="s">
+      <c r="E31" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="D5:D10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="D15:D19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D052A39-4282-404B-9441-7B4B3D702788}">
+  <dimension ref="B2:F19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="9.140625" style="66"/>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
+    <col min="4" max="4" width="62.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="105.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6">
+      <c r="B2" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="66">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D5" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="24">
-      <c r="A10" s="13" t="s">
+    </row>
+    <row r="6" spans="2:6">
+      <c r="D6" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="16" t="s">
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="66">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D7" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="24">
-      <c r="A11" s="13" t="s">
+    </row>
+    <row r="8" spans="2:6">
+      <c r="D8" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="16" t="s">
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="66">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>61</v>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="66">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="D11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="D12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="D13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="66">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="66">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5251586E-7A0B-458B-9C7E-4A9927656309}">
+  <dimension ref="A2:N14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="66"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14">
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="66">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="N5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="N6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="C7" t="s">
+        <v>108</v>
+      </c>
+      <c r="N7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="66">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="N10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="N11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="N12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="66">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>113</v>
+      </c>
+      <c r="L14">
+        <v>3</v>
+      </c>
+      <c r="M14" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2282,144 +3548,478 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2FDF3D-9DCF-468A-B750-490B7A55F874}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8ABEF94-B3DE-46A7-AA17-C522D7D14E74}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="81.5703125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="90.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="36">
-      <c r="A1" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>91</v>
+    <row r="1" spans="1:10" ht="15.6" customHeight="1">
+      <c r="A1" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="12" customHeight="1">
+      <c r="A2" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" customHeight="1">
+      <c r="A3" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A4" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="12" customHeight="1">
+      <c r="A5" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="12" customHeight="1">
+      <c r="A6" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="12" customHeight="1">
+      <c r="A7" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="12" customHeight="1">
+      <c r="A8" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="13.5">
+      <c r="A13" s="52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="13.5">
+      <c r="A14" s="52" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.5">
+      <c r="A15" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.5">
+      <c r="A16" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J8" xr:uid="{B8ABEF94-B3DE-46A7-AA17-C522D7D14E74}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J8">
+      <sortCondition ref="B1:B8"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDDE129A-6F78-40FC-80D5-4234A2C10785}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" style="50" customWidth="1"/>
+    <col min="2" max="2" width="59.85546875" style="50" customWidth="1"/>
+    <col min="3" max="4" width="49.85546875" style="50" customWidth="1"/>
+    <col min="5" max="5" width="52.5703125" style="50" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="27">
+      <c r="A2" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="51" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" customHeight="1">
+      <c r="A3" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="25.5" customHeight="1">
+      <c r="A4" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="51" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A5" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A6" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="51" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="52.5" customHeight="1">
+      <c r="A7" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="23.45" customHeight="1">
+      <c r="A8" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="52" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="52" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="52" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2427,51 +4027,686 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5852E5E1-844F-4DD4-9238-FB9FDE91978F}">
-  <dimension ref="A2:B5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C2FDF3D-9DCF-468A-B750-490B7A55F874}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="17" customWidth="1"/>
+    <col min="3" max="5" width="15.42578125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="17" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" style="17" customWidth="1"/>
+    <col min="8" max="8" width="9.85546875" style="17" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="3.42578125" style="17" customWidth="1"/>
+    <col min="11" max="11" width="34.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="15">
-      <c r="A2" s="54" t="s">
-        <v>93</v>
+    <row r="1" spans="1:11">
+      <c r="A1" s="17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="97" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="97"/>
+      <c r="B3" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="97"/>
+      <c r="B4" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="97"/>
+      <c r="B5" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="97"/>
+      <c r="B6" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="97"/>
+      <c r="B7" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="97"/>
+      <c r="B8" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="12" customHeight="1">
+      <c r="A9" s="97"/>
+      <c r="B9" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="J9" s="98" t="s">
+        <v>194</v>
+      </c>
+      <c r="K9" s="99"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="97"/>
+      <c r="B10" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="J10" s="98"/>
+      <c r="K10" s="99"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="97"/>
+      <c r="B11" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="J11" s="98"/>
+      <c r="K11" s="99"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="97"/>
+      <c r="B12" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" s="98"/>
+      <c r="K12" s="99"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="97"/>
+      <c r="B13" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="98"/>
+      <c r="K13" s="99"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="97" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="97"/>
+      <c r="B16" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="97"/>
+      <c r="B17" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="97"/>
+      <c r="B18" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="97"/>
+      <c r="B19" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="97"/>
+      <c r="B20" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="97"/>
+      <c r="B21" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="97"/>
+      <c r="B22" s="43" t="s">
+        <v>193</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="97"/>
+      <c r="B23" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="97"/>
+      <c r="B24" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="97"/>
+      <c r="B25" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="97"/>
+      <c r="B26" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="A15:A26"/>
+    <mergeCell ref="J9:K13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5852E5E1-844F-4DD4-9238-FB9FDE91978F}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="12"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" style="29" customWidth="1"/>
+    <col min="2" max="2" width="95" style="29" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="55" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="55" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="56" t="s">
+        <v>125</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15">
-      <c r="A3" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15">
-      <c r="A4" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15">
-      <c r="A5" s="53" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>97</v>
-      </c>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="12" customHeight="1">
+      <c r="A3" s="56" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="12" customHeight="1">
+      <c r="A4" s="56" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="54" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="54" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="53"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="53"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="53"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" tooltip="https://www.linkedin.com/learning/role-play/scenarios/urn:li:la_roleplayscenario:urn:li:llsservescenario:127535744?u=236676260" xr:uid="{C4C4580A-F2F4-4226-A783-EB9FBA6E7E3F}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{5EF6DF48-00B4-4886-992F-A054FC85254B}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{CDDCF471-E4CB-4998-8DEC-BD837207AA73}"/>
+    <hyperlink ref="B5" r:id="rId1" tooltip="https://www.linkedin.com/learning/role-play/scenarios/urn:li:la_roleplayscenario:urn:li:llsservescenario:127536712?u=236676260" display="https://www.linkedin.com/learning/role-play/scenarios/urn:li:la_rolePlayScenario:urn:li:llsServeScenario:127536712?u=236676260" xr:uid="{1497FD4A-A26B-4D58-AB66-FAAE66215C96}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{CDDCF471-E4CB-4998-8DEC-BD837207AA73}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{5EF6DF48-00B4-4886-992F-A054FC85254B}"/>
+    <hyperlink ref="B3" r:id="rId4" tooltip="https://www.linkedin.com/learning/role-play/scenarios/urn:li:la_roleplayscenario:urn:li:llsservescenario:127535744?u=236676260" xr:uid="{C4C4580A-F2F4-4226-A783-EB9FBA6E7E3F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
